--- a/AAII_Financials/Quarterly/CNTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="92">
   <si>
     <t>CNTX</t>
   </si>
@@ -656,135 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -827,8 +831,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -872,8 +876,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -961,8 +968,11 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1050,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1096,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>2100</v>
       </c>
       <c r="R12" s="3">
         <v>2100</v>
       </c>
       <c r="S12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T12" s="3">
         <v>2000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,8 +1278,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1317,15 +1337,15 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,8 +1358,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1350,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1439,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1495,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3900</v>
-      </c>
-      <c r="R17" s="3">
-        <v>4000</v>
       </c>
       <c r="S17" s="3">
         <v>4000</v>
       </c>
       <c r="T17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U17" s="3">
         <v>3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>800</v>
       </c>
       <c r="Y17" s="3">
         <v>800</v>
       </c>
       <c r="Z17" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AA17" s="3">
         <v>700</v>
       </c>
       <c r="AB17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-4000</v>
       </c>
       <c r="S18" s="3">
         <v>-4000</v>
       </c>
       <c r="T18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="U18" s="3">
         <v>-3400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-800</v>
       </c>
       <c r="Y18" s="3">
         <v>-800</v>
       </c>
       <c r="Z18" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="AA18" s="3">
         <v>-700</v>
       </c>
       <c r="AB18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,13 +1713,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1695,7 +1729,7 @@
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1713,11 +1747,11 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1725,14 +1759,14 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1749,85 +1783,88 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>8300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-18700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1858,8 +1895,11 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1917,14 +1957,14 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -1933,111 +1973,117 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>300</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>7500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2080,8 +2126,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2125,8 +2171,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2263,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,13 +2815,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -2763,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -2781,11 +2851,11 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2793,14 +2863,14 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2817,117 +2887,123 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3091,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,77 +3350,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E41" s="3">
         <v>54500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>66000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3440,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3442,8 +3532,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3486,8 +3579,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3531,8 +3624,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3575,8 +3671,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3620,8 +3716,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3643,8 +3742,8 @@
       <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -3664,32 +3763,32 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1600</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
+      <c r="Y45" s="3">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
@@ -3709,77 +3808,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E46" s="3">
         <v>58500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>68400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>79100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>97900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>86100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>102700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>37900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>41900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>51300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1700</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +3900,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3842,8 +3947,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3887,8 +3992,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3896,10 +4004,10 @@
         <v>300</v>
       </c>
       <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>200</v>
@@ -3911,11 +4019,11 @@
         <v>200</v>
       </c>
       <c r="J48" s="3">
+        <v>200</v>
+      </c>
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
@@ -3929,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -3941,11 +4049,11 @@
         <v>100</v>
       </c>
       <c r="T48" s="3">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3958,8 +4066,8 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3976,8 +4084,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4065,8 +4176,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,8 +4360,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4281,8 +4401,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4294,26 +4414,26 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
-      </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,77 +4544,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E54" s="3">
         <v>58900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>93000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>98100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>86300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>102700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>51300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,77 +4706,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E57" s="3">
         <v>2500</v>
       </c>
       <c r="F57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1200</v>
       </c>
       <c r="P57" s="3">
         <v>1200</v>
       </c>
       <c r="Q57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1900</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4796,11 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4674,7 +4808,7 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
@@ -4692,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4728,13 +4862,13 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>100</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
@@ -4754,17 +4888,20 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
@@ -4772,17 +4909,17 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
@@ -4790,41 +4927,41 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
       <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
         <v>2300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1200</v>
       </c>
       <c r="U59" s="3">
         <v>1200</v>
       </c>
       <c r="V59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W59" s="3">
         <v>1300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,77 +4980,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
-      </c>
-      <c r="P60" s="3">
-        <v>3200</v>
       </c>
       <c r="Q60" s="3">
         <v>3200</v>
       </c>
       <c r="R60" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3300</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,8 +5072,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4941,13 +5084,13 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>100</v>
@@ -4959,7 +5102,7 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5021,8 +5164,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5065,20 +5211,20 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -5092,8 +5238,8 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -5110,8 +5256,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,77 +5532,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3800</v>
-      </c>
-      <c r="P66" s="3">
-        <v>3200</v>
       </c>
       <c r="Q66" s="3">
         <v>3200</v>
       </c>
       <c r="R66" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S66" s="3">
         <v>4000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5737,17 +5905,17 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>21000</v>
       </c>
       <c r="X70" s="3">
+        <v>21000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>16300</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5766,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,77 +6026,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-154100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-139600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-130900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-117900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-108200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-99400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-94800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-91400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-74000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-68100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-61300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-55400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-50400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-44100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-40500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-36700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-32700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-29300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-26200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-24700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,77 +6394,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E76" s="3">
         <v>52200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>60500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>73200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>82500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>91000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>95300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>101100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>38100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-23100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-22200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6578,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6646,17 +6845,17 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -6673,8 +6872,8 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6694,8 +6893,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7353,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5000</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-2100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,8 +7481,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7287,8 +7508,8 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
@@ -7305,8 +7526,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7323,8 +7544,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -7332,8 +7553,8 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7350,8 +7571,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,20 +7755,23 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-4500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
@@ -7552,11 +7782,11 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7572,15 +7802,15 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
@@ -7590,8 +7820,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -7599,8 +7829,8 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -7617,8 +7847,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7694,8 +7928,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7739,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,16 +8249,19 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -8027,17 +8273,17 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>14500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>94800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8050,8 +8296,8 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -8060,34 +8306,34 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>54200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
@@ -8095,8 +8341,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8139,8 +8388,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8184,8 +8433,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8193,84 +8445,87 @@
         <v>-11500</v>
       </c>
       <c r="E102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>91400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>49300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
